--- a/research/traditional_assets/database/data/bermuda/bermuda_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_drugs_pharmaceutical.xlsx
@@ -587,8 +587,23 @@
           <t>Drugs (Pharmaceutical)</t>
         </is>
       </c>
+      <c r="G2">
+        <v>-5.525925925925926</v>
+      </c>
+      <c r="H2">
+        <v>-12.59259259259259</v>
+      </c>
+      <c r="I2">
+        <v>-12.88707801633228</v>
+      </c>
+      <c r="J2">
+        <v>-12.88707801633228</v>
+      </c>
       <c r="K2">
-        <v>-13.3</v>
+        <v>-18.8</v>
+      </c>
+      <c r="L2">
+        <v>-13.92592592592593</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>9.16</v>
+        <v>0.391</v>
       </c>
       <c r="V2">
-        <v>0.3405204460966543</v>
+        <v>0.06895943562610229</v>
       </c>
       <c r="W2">
-        <v>-2.81183932346723</v>
+        <v>-0.8663594470046083</v>
       </c>
       <c r="X2">
-        <v>0.06448616467289633</v>
+        <v>0.1833475695028082</v>
       </c>
       <c r="Y2">
-        <v>-2.876325488140127</v>
+        <v>-1.049707016507416</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>0.1076316705582989</v>
       </c>
       <c r="AA2">
-        <v>-2.113195936227301</v>
+        <v>-1.387057735512972</v>
       </c>
       <c r="AB2">
-        <v>0.06448169112087208</v>
+        <v>0.1328114385822352</v>
       </c>
       <c r="AC2">
-        <v>-2.177677627348173</v>
+        <v>-1.519869174095207</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="AE2">
-        <v>0.02735635454545917</v>
+        <v>0.002776610242889712</v>
       </c>
       <c r="AF2">
-        <v>0.02735635454545917</v>
+        <v>5.47277661024289</v>
       </c>
       <c r="AG2">
-        <v>-9.132643645454541</v>
+        <v>5.08177661024289</v>
       </c>
       <c r="AH2">
-        <v>0.001015931686173169</v>
+        <v>0.4911501685506369</v>
       </c>
       <c r="AI2">
-        <v>0.001259074233379345</v>
+        <v>0.4050075545609511</v>
       </c>
       <c r="AJ2">
-        <v>-0.5140125217963628</v>
+        <v>0.4726452933742724</v>
       </c>
       <c r="AK2">
-        <v>-0.7266956858553133</v>
+        <v>0.387278092074517</v>
       </c>
       <c r="AL2">
-        <v>0.329</v>
+        <v>0.413</v>
       </c>
       <c r="AM2">
-        <v>0.329</v>
+        <v>0.41</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>-0.3144220267862275</v>
       </c>
       <c r="AO2">
-        <v>-30.69908814589665</v>
+        <v>-42.13075060532687</v>
       </c>
       <c r="AP2">
-        <v>0.9159205340943276</v>
+        <v>-0.2921064902134213</v>
       </c>
       <c r="AQ2">
-        <v>-30.69908814589665</v>
+        <v>-42.4390243902439</v>
       </c>
     </row>
     <row r="3">
@@ -697,8 +712,23 @@
           <t>Drugs (Pharmaceutical)</t>
         </is>
       </c>
+      <c r="G3">
+        <v>-5.525925925925926</v>
+      </c>
+      <c r="H3">
+        <v>-12.59259259259259</v>
+      </c>
+      <c r="I3">
+        <v>-12.88707801633228</v>
+      </c>
+      <c r="J3">
+        <v>-12.88707801633228</v>
+      </c>
       <c r="K3">
-        <v>-13.3</v>
+        <v>-18.8</v>
+      </c>
+      <c r="L3">
+        <v>-13.92592592592593</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>9.16</v>
+        <v>0.391</v>
       </c>
       <c r="V3">
-        <v>0.3405204460966543</v>
+        <v>0.06895943562610229</v>
       </c>
       <c r="W3">
-        <v>-2.81183932346723</v>
+        <v>-0.8663594470046083</v>
       </c>
       <c r="X3">
-        <v>0.06448616467289633</v>
+        <v>0.1833475695028082</v>
       </c>
       <c r="Y3">
-        <v>-2.876325488140127</v>
+        <v>-1.049707016507416</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.1076316705582989</v>
       </c>
       <c r="AA3">
-        <v>-2.113195936227301</v>
+        <v>-1.387057735512972</v>
       </c>
       <c r="AB3">
-        <v>0.06448169112087208</v>
+        <v>0.1328114385822352</v>
       </c>
       <c r="AC3">
-        <v>-2.177677627348173</v>
+        <v>-1.519869174095207</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="AE3">
-        <v>0.02735635454545917</v>
+        <v>0.002776610242889712</v>
       </c>
       <c r="AF3">
-        <v>0.02735635454545917</v>
+        <v>5.47277661024289</v>
       </c>
       <c r="AG3">
-        <v>-9.132643645454541</v>
+        <v>5.08177661024289</v>
       </c>
       <c r="AH3">
-        <v>0.001015931686173169</v>
+        <v>0.4911501685506369</v>
       </c>
       <c r="AI3">
-        <v>0.001259074233379345</v>
+        <v>0.4050075545609511</v>
       </c>
       <c r="AJ3">
-        <v>-0.5140125217963628</v>
+        <v>0.4726452933742724</v>
       </c>
       <c r="AK3">
-        <v>-0.7266956858553133</v>
+        <v>0.387278092074517</v>
       </c>
       <c r="AL3">
-        <v>0.329</v>
+        <v>0.413</v>
       </c>
       <c r="AM3">
-        <v>0.329</v>
+        <v>0.41</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>-0.3144220267862275</v>
       </c>
       <c r="AO3">
-        <v>-30.69908814589665</v>
+        <v>-42.13075060532687</v>
       </c>
       <c r="AP3">
-        <v>0.9159205340943276</v>
+        <v>-0.2921064902134213</v>
       </c>
       <c r="AQ3">
-        <v>-30.69908814589665</v>
+        <v>-42.4390243902439</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bermuda/bermuda_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_drugs_pharmaceutical.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-5.525925925925926</v>
+        <v>42.53731343283582</v>
       </c>
       <c r="H2">
-        <v>-12.59259259259259</v>
+        <v>-110.4477611940299</v>
       </c>
       <c r="I2">
-        <v>-12.88707801633228</v>
+        <v>-82.81738441644474</v>
       </c>
       <c r="J2">
-        <v>-12.88707801633228</v>
+        <v>-82.81738441644474</v>
       </c>
       <c r="K2">
-        <v>-18.8</v>
+        <v>-26.5</v>
       </c>
       <c r="L2">
-        <v>-13.92592592592593</v>
+        <v>-197.7611940298507</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.391</v>
+        <v>0.056</v>
       </c>
       <c r="V2">
-        <v>0.06895943562610229</v>
+        <v>0.04057971014492754</v>
       </c>
       <c r="W2">
-        <v>-0.8663594470046083</v>
+        <v>-3.753541076487252</v>
       </c>
       <c r="X2">
-        <v>0.1833475695028082</v>
+        <v>0.2352484627379883</v>
       </c>
       <c r="Y2">
-        <v>-1.049707016507416</v>
+        <v>-3.988789539225241</v>
       </c>
       <c r="Z2">
-        <v>0.1076316705582989</v>
+        <v>0.01103639348355768</v>
       </c>
       <c r="AA2">
-        <v>-1.387057735512972</v>
+        <v>-0.9140052416989417</v>
       </c>
       <c r="AB2">
-        <v>0.1328114385822352</v>
+        <v>0.159951087111174</v>
       </c>
       <c r="AC2">
-        <v>-1.519869174095207</v>
+        <v>-1.073956328810116</v>
       </c>
       <c r="AD2">
-        <v>5.47</v>
+        <v>3.87</v>
       </c>
       <c r="AE2">
-        <v>0.002776610242889712</v>
+        <v>0.002647559017983401</v>
       </c>
       <c r="AF2">
-        <v>5.47277661024289</v>
+        <v>3.872647559017984</v>
       </c>
       <c r="AG2">
-        <v>5.08177661024289</v>
+        <v>3.816647559017984</v>
       </c>
       <c r="AH2">
-        <v>0.4911501685506369</v>
+        <v>0.737275348384882</v>
       </c>
       <c r="AI2">
-        <v>0.4050075545609511</v>
+        <v>2.113143653814771</v>
       </c>
       <c r="AJ2">
-        <v>0.4726452933742724</v>
+        <v>0.7344441807285503</v>
       </c>
       <c r="AK2">
-        <v>0.387278092074517</v>
+        <v>2.148229984976638</v>
       </c>
       <c r="AL2">
-        <v>0.413</v>
+        <v>1.19</v>
       </c>
       <c r="AM2">
-        <v>0.41</v>
+        <v>1.189</v>
       </c>
       <c r="AN2">
-        <v>-0.3144220267862275</v>
+        <v>1290</v>
       </c>
       <c r="AO2">
-        <v>-42.13075060532687</v>
+        <v>-9.327731092436975</v>
       </c>
       <c r="AP2">
-        <v>-0.2921064902134213</v>
+        <v>1272.215853005994</v>
       </c>
       <c r="AQ2">
-        <v>-42.4390243902439</v>
+        <v>-9.335576114381833</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-5.525925925925926</v>
+        <v>42.53731343283582</v>
       </c>
       <c r="H3">
-        <v>-12.59259259259259</v>
+        <v>-110.4477611940299</v>
       </c>
       <c r="I3">
-        <v>-12.88707801633228</v>
+        <v>-82.81738441644474</v>
       </c>
       <c r="J3">
-        <v>-12.88707801633228</v>
+        <v>-82.81738441644474</v>
       </c>
       <c r="K3">
-        <v>-18.8</v>
+        <v>-26.5</v>
       </c>
       <c r="L3">
-        <v>-13.92592592592593</v>
+        <v>-197.7611940298507</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.391</v>
+        <v>0.056</v>
       </c>
       <c r="V3">
-        <v>0.06895943562610229</v>
+        <v>0.04057971014492754</v>
       </c>
       <c r="W3">
-        <v>-0.8663594470046083</v>
+        <v>-3.753541076487252</v>
       </c>
       <c r="X3">
-        <v>0.1833475695028082</v>
+        <v>0.2352484627379883</v>
       </c>
       <c r="Y3">
-        <v>-1.049707016507416</v>
+        <v>-3.988789539225241</v>
       </c>
       <c r="Z3">
-        <v>0.1076316705582989</v>
+        <v>0.01103639348355768</v>
       </c>
       <c r="AA3">
-        <v>-1.387057735512972</v>
+        <v>-0.9140052416989417</v>
       </c>
       <c r="AB3">
-        <v>0.1328114385822352</v>
+        <v>0.159951087111174</v>
       </c>
       <c r="AC3">
-        <v>-1.519869174095207</v>
+        <v>-1.073956328810116</v>
       </c>
       <c r="AD3">
-        <v>5.47</v>
+        <v>3.87</v>
       </c>
       <c r="AE3">
-        <v>0.002776610242889712</v>
+        <v>0.002647559017983401</v>
       </c>
       <c r="AF3">
-        <v>5.47277661024289</v>
+        <v>3.872647559017984</v>
       </c>
       <c r="AG3">
-        <v>5.08177661024289</v>
+        <v>3.816647559017984</v>
       </c>
       <c r="AH3">
-        <v>0.4911501685506369</v>
+        <v>0.737275348384882</v>
       </c>
       <c r="AI3">
-        <v>0.4050075545609511</v>
+        <v>2.113143653814771</v>
       </c>
       <c r="AJ3">
-        <v>0.4726452933742724</v>
+        <v>0.7344441807285503</v>
       </c>
       <c r="AK3">
-        <v>0.387278092074517</v>
+        <v>2.148229984976638</v>
       </c>
       <c r="AL3">
-        <v>0.413</v>
+        <v>1.19</v>
       </c>
       <c r="AM3">
-        <v>0.41</v>
+        <v>1.189</v>
       </c>
       <c r="AN3">
-        <v>-0.3144220267862275</v>
+        <v>1290</v>
       </c>
       <c r="AO3">
-        <v>-42.13075060532687</v>
+        <v>-9.327731092436975</v>
       </c>
       <c r="AP3">
-        <v>-0.2921064902134213</v>
+        <v>1272.215853005994</v>
       </c>
       <c r="AQ3">
-        <v>-42.4390243902439</v>
+        <v>-9.335576114381833</v>
       </c>
     </row>
   </sheetData>
